--- a/rollforever/Assets/Excels/WeaponConfig.xlsx
+++ b/rollforever/Assets/Excels/WeaponConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\rollforever\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00180DB1-00D2-4E78-BE49-92EEAC91EB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D11F597-E3B9-4F7F-B3B4-3C4C2CE4B6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9892" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4250" yWindow="1270" windowWidth="14400" windowHeight="8210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="baseData" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>name</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>Mũi tên</t>
+  </si>
+  <si>
+    <t>attack_range</t>
   </si>
 </sst>
 </file>
@@ -382,27 +385,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.4609375" customWidth="1"/>
-    <col min="2" max="2" width="9.921875" customWidth="1"/>
-    <col min="3" max="3" width="19.3828125" customWidth="1"/>
-    <col min="4" max="4" width="11.23046875" customWidth="1"/>
-    <col min="5" max="5" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.3828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.23046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.4609375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.61328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.84375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.3828125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="9.90625" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" customWidth="1"/>
+    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -416,15 +420,17 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -432,8 +438,9 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2001</v>
       </c>
@@ -444,12 +451,15 @@
         <v>20101</v>
       </c>
       <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
         <v>12</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1.05</v>
       </c>
     </row>

--- a/rollforever/Assets/Excels/WeaponConfig.xlsx
+++ b/rollforever/Assets/Excels/WeaponConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\rollforever\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D11F597-E3B9-4F7F-B3B4-3C4C2CE4B6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBB98DD-069B-4A84-9DCC-6420781B49DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4250" yWindow="1270" windowWidth="14400" windowHeight="8210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>address_prefab</t>
-  </si>
-  <si>
     <t>skill_id</t>
   </si>
   <si>
@@ -45,13 +42,13 @@
     <t>attack_rate</t>
   </si>
   <si>
-    <t>weaponId</t>
-  </si>
-  <si>
     <t>Mũi tên</t>
   </si>
   <si>
     <t>attack_range</t>
+  </si>
+  <si>
+    <t>weapon_id</t>
   </si>
 </sst>
 </file>
@@ -385,30 +382,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.453125" customWidth="1"/>
     <col min="2" max="2" width="9.90625" customWidth="1"/>
-    <col min="3" max="3" width="19.36328125" customWidth="1"/>
-    <col min="4" max="4" width="11.26953125" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -417,10 +413,10 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -428,9 +424,7 @@
       <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -438,28 +432,27 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2001</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>20101</v>
       </c>
       <c r="D2">
-        <v>20101</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
         <v>1.05</v>
       </c>
     </row>

--- a/rollforever/Assets/Excels/WeaponConfig.xlsx
+++ b/rollforever/Assets/Excels/WeaponConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\rollforever\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBB98DD-069B-4A84-9DCC-6420781B49DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7A3137-B5A7-4287-BD77-0E0004E35B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4250" yWindow="1270" windowWidth="14400" windowHeight="8210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>name</t>
   </si>
@@ -49,6 +49,12 @@
   </si>
   <si>
     <t>weapon_id</t>
+  </si>
+  <si>
+    <t>base_price</t>
+  </si>
+  <si>
+    <t>price_linear</t>
   </si>
 </sst>
 </file>
@@ -382,27 +388,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.453125" customWidth="1"/>
     <col min="2" max="2" width="9.90625" customWidth="1"/>
     <col min="3" max="3" width="11.26953125" customWidth="1"/>
-    <col min="4" max="4" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -413,27 +421,33 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2001</v>
       </c>
@@ -444,15 +458,21 @@
         <v>20101</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>5</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>12</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>1.05</v>
       </c>
     </row>
